--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L666"/>
+  <dimension ref="A1:L669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28420,6 +28420,132 @@
       <c r="L666" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="C667" t="n">
+        <v>354.52</v>
+      </c>
+      <c r="D667" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="E667" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="F667" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="G667" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="H667" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="I667" t="n">
+        <v>360.88</v>
+      </c>
+      <c r="J667" t="n">
+        <v>344.74</v>
+      </c>
+      <c r="K667" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>353.65</v>
+      </c>
+      <c r="C668" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="D668" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="E668" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="F668" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="G668" t="n">
+        <v>349.64</v>
+      </c>
+      <c r="H668" t="n">
+        <v>352.42</v>
+      </c>
+      <c r="I668" t="n">
+        <v>361</v>
+      </c>
+      <c r="J668" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="K668" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="C669" t="n">
+        <v>353.26</v>
+      </c>
+      <c r="D669" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="E669" t="n">
+        <v>351.34</v>
+      </c>
+      <c r="F669" t="n">
+        <v>350.24</v>
+      </c>
+      <c r="G669" t="n">
+        <v>349.34</v>
+      </c>
+      <c r="H669" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="I669" t="n">
+        <v>360.65</v>
+      </c>
+      <c r="J669" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="K669" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28434,7 +28560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35877,6 +36003,36 @@
       </c>
       <c r="B744" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -36045,28 +36201,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.160572855869008</v>
+        <v>-0.1590288834471212</v>
       </c>
       <c r="J2" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K2" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1249810473063894</v>
+        <v>0.1236489192764828</v>
       </c>
       <c r="M2" t="n">
-        <v>2.357885020710475</v>
+        <v>2.355719383522337</v>
       </c>
       <c r="N2" t="n">
-        <v>8.628124793402939</v>
+        <v>8.602914691673091</v>
       </c>
       <c r="O2" t="n">
-        <v>2.93736698309948</v>
+        <v>2.933072568429409</v>
       </c>
       <c r="P2" t="n">
-        <v>356.1848737632423</v>
+        <v>356.1669104820844</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36127,28 +36283,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1303583220014557</v>
+        <v>-0.1321921814759937</v>
       </c>
       <c r="J3" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K3" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L3" t="n">
-        <v>0.108238030160511</v>
+        <v>0.1115259135117811</v>
       </c>
       <c r="M3" t="n">
-        <v>1.874294666364408</v>
+        <v>1.875179137884334</v>
       </c>
       <c r="N3" t="n">
-        <v>6.691838405987579</v>
+        <v>6.68168981551714</v>
       </c>
       <c r="O3" t="n">
-        <v>2.586858791273227</v>
+        <v>2.584896480619125</v>
       </c>
       <c r="P3" t="n">
-        <v>359.4893218386789</v>
+        <v>359.5106587788805</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36209,28 +36365,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1351613717350299</v>
+        <v>-0.1383317706679916</v>
       </c>
       <c r="J4" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K4" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08480777935702322</v>
+        <v>0.08869672621871771</v>
       </c>
       <c r="M4" t="n">
-        <v>2.206490181017038</v>
+        <v>2.212947012426119</v>
       </c>
       <c r="N4" t="n">
-        <v>9.422814991526968</v>
+        <v>9.436370999775482</v>
       </c>
       <c r="O4" t="n">
-        <v>3.069660403290072</v>
+        <v>3.071867672894697</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0905926841181</v>
+        <v>359.1274773141325</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36291,28 +36447,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1475706786526068</v>
+        <v>-0.1528014624578205</v>
       </c>
       <c r="J5" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K5" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1186486957504572</v>
+        <v>0.1249473778125878</v>
       </c>
       <c r="M5" t="n">
-        <v>2.130369187387978</v>
+        <v>2.148136419070438</v>
       </c>
       <c r="N5" t="n">
-        <v>7.731879669624045</v>
+        <v>7.848159869333815</v>
       </c>
       <c r="O5" t="n">
-        <v>2.780625769431055</v>
+        <v>2.801456740578697</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0119121184725</v>
+        <v>361.0727649082831</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36373,28 +36529,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1034614786941715</v>
+        <v>-0.1084979850482826</v>
       </c>
       <c r="J6" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K6" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04914207008391103</v>
+        <v>0.05350308964445472</v>
       </c>
       <c r="M6" t="n">
-        <v>2.439964382653716</v>
+        <v>2.455992651923155</v>
       </c>
       <c r="N6" t="n">
-        <v>9.899617224291122</v>
+        <v>9.995153761349068</v>
       </c>
       <c r="O6" t="n">
-        <v>3.146365716869405</v>
+        <v>3.161511309698112</v>
       </c>
       <c r="P6" t="n">
-        <v>358.5117023940439</v>
+        <v>358.5702949553074</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36455,28 +36611,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07401730036419811</v>
+        <v>-0.07913861165286176</v>
       </c>
       <c r="J7" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K7" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03047906431057079</v>
+        <v>0.03440227276314056</v>
       </c>
       <c r="M7" t="n">
-        <v>2.194676874910071</v>
+        <v>2.214853198320633</v>
       </c>
       <c r="N7" t="n">
-        <v>8.329537694012917</v>
+        <v>8.437071883357921</v>
       </c>
       <c r="O7" t="n">
-        <v>2.886093847055725</v>
+        <v>2.904663815892972</v>
       </c>
       <c r="P7" t="n">
-        <v>357.0060997468262</v>
+        <v>357.065679067755</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36537,28 +36693,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02483813039408849</v>
+        <v>0.0207859299664831</v>
       </c>
       <c r="J8" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K8" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003566052850452972</v>
+        <v>0.002494289281442907</v>
       </c>
       <c r="M8" t="n">
-        <v>2.164334694730182</v>
+        <v>2.177135993176999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.239434384200571</v>
+        <v>8.293030923542743</v>
       </c>
       <c r="O8" t="n">
-        <v>2.870441496390506</v>
+        <v>2.879762303306081</v>
       </c>
       <c r="P8" t="n">
-        <v>356.2524212936028</v>
+        <v>356.2995630304601</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -36619,28 +36775,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0931035678691611</v>
+        <v>0.08992044238491588</v>
       </c>
       <c r="J9" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K9" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03552640094148152</v>
+        <v>0.03333618806630734</v>
       </c>
       <c r="M9" t="n">
-        <v>2.52536426881025</v>
+        <v>2.528842074292162</v>
       </c>
       <c r="N9" t="n">
-        <v>11.24787895381613</v>
+        <v>11.25335936757348</v>
       </c>
       <c r="O9" t="n">
-        <v>3.353785764448309</v>
+        <v>3.354602713820741</v>
       </c>
       <c r="P9" t="n">
-        <v>361.9525224245422</v>
+        <v>361.9895543085614</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -36701,28 +36857,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1359501465867763</v>
+        <v>0.1321905032637029</v>
       </c>
       <c r="J10" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K10" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06259473550866157</v>
+        <v>0.05953683252438502</v>
       </c>
       <c r="M10" t="n">
-        <v>2.737688451763308</v>
+        <v>2.741893151412646</v>
       </c>
       <c r="N10" t="n">
-        <v>13.22963293126322</v>
+        <v>13.24836769326075</v>
       </c>
       <c r="O10" t="n">
-        <v>3.637256236679403</v>
+        <v>3.639830723160179</v>
       </c>
       <c r="P10" t="n">
-        <v>345.1476988835895</v>
+        <v>345.1914380142589</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -36783,28 +36939,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1655688267629506</v>
+        <v>0.1612493495224513</v>
       </c>
       <c r="J11" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="K11" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0815189227542028</v>
+        <v>0.07776604438323698</v>
       </c>
       <c r="M11" t="n">
-        <v>2.919451796860213</v>
+        <v>2.925120475243709</v>
       </c>
       <c r="N11" t="n">
-        <v>14.76276744784267</v>
+        <v>14.79969745860139</v>
       </c>
       <c r="O11" t="n">
-        <v>3.842234694529041</v>
+        <v>3.847037491187392</v>
       </c>
       <c r="P11" t="n">
-        <v>338.7307799303632</v>
+        <v>338.7810322749912</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -36846,7 +37002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L666"/>
+  <dimension ref="A1:L669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78141,6 +78297,192 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-36.778138708780865,175.00932586597335</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-36.77886553179767,175.00933864736854</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-36.77955752612873,175.00957167550646</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-36.78022101756404,175.00995948367617</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-36.78081081428339,175.01048592761748</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-36.78135350470996,175.01108459501526</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-36.781867243353865,175.01171463019259</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-36.78233890548478,175.01239305278847</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-36.78278212164165,175.0131244158912</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>-36.783144975079395,175.01390447707058</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-36.778138673018304,175.00932911426736</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-36.77886584462379,175.0093362137673</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-36.779557594038856,175.00957146797535</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-36.78021987673577,175.00996176775308</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-36.78080959725238,175.010487729067</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-36.78135006986998,175.0110891908563</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-36.781866749033384,175.01171528252448</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-36.78233802638664,175.0123938355932</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-36.78278359245926,175.013123565757</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>-36.78314611905109,175.0139038158598</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-36.7781386199909,175.00933393070326</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-36.778867323437446,175.00932470947043</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-36.779559801118026,175.00956472321366</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-36.78022020947735,175.009961101564</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-36.78080965520623,175.01048764328368</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-36.781351909962844,175.01108672879866</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-36.78186693440355,175.01171503790002</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-36.78234059042288,175.01239155241268</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-36.78278604382192,175.01312214886661</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>-36.78314987781515,175.01390164331002</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L669"/>
+  <dimension ref="A1:L671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28544,6 +28544,90 @@
         <v>337.9</v>
       </c>
       <c r="L669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="C670" t="n">
+        <v>352.13</v>
+      </c>
+      <c r="D670" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="E670" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="F670" t="n">
+        <v>350.59</v>
+      </c>
+      <c r="G670" t="n">
+        <v>348.33</v>
+      </c>
+      <c r="H670" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="I670" t="n">
+        <v>359.82</v>
+      </c>
+      <c r="J670" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="K670" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="C671" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="D671" t="n">
+        <v>353.86</v>
+      </c>
+      <c r="E671" t="n">
+        <v>354.13</v>
+      </c>
+      <c r="F671" t="n">
+        <v>350.71</v>
+      </c>
+      <c r="G671" t="n">
+        <v>348.59</v>
+      </c>
+      <c r="H671" t="n">
+        <v>351.14</v>
+      </c>
+      <c r="I671" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="J671" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="K671" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="L671" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28560,7 +28644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B747"/>
+  <dimension ref="A1:B749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36033,6 +36117,26 @@
       </c>
       <c r="B747" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -36201,28 +36305,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1590288834471212</v>
+        <v>-0.1562613044495569</v>
       </c>
       <c r="J2" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K2" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1236489192764828</v>
+        <v>0.1197192565268114</v>
       </c>
       <c r="M2" t="n">
-        <v>2.355719383522337</v>
+        <v>2.363638636841922</v>
       </c>
       <c r="N2" t="n">
-        <v>8.602914691673091</v>
+        <v>8.64121714157706</v>
       </c>
       <c r="O2" t="n">
-        <v>2.933072568429409</v>
+        <v>2.939594724035451</v>
       </c>
       <c r="P2" t="n">
-        <v>356.1669104820844</v>
+        <v>356.1346119113899</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36283,28 +36387,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1321921814759937</v>
+        <v>-0.13434688298891</v>
       </c>
       <c r="J3" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K3" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1115259135117811</v>
+        <v>0.1147663220912347</v>
       </c>
       <c r="M3" t="n">
-        <v>1.875179137884334</v>
+        <v>1.880402785286566</v>
       </c>
       <c r="N3" t="n">
-        <v>6.68168981551714</v>
+        <v>6.700596875683834</v>
       </c>
       <c r="O3" t="n">
-        <v>2.584896480619125</v>
+        <v>2.588551115138319</v>
       </c>
       <c r="P3" t="n">
-        <v>359.5106587788805</v>
+        <v>359.5358027700044</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36365,28 +36469,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1383317706679916</v>
+        <v>-0.1394092953899895</v>
       </c>
       <c r="J4" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K4" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08869672621871771</v>
+        <v>0.0903477217152574</v>
       </c>
       <c r="M4" t="n">
-        <v>2.212947012426119</v>
+        <v>2.211916685973201</v>
       </c>
       <c r="N4" t="n">
-        <v>9.436370999775482</v>
+        <v>9.41795275788297</v>
       </c>
       <c r="O4" t="n">
-        <v>3.071867672894697</v>
+        <v>3.068868318759046</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1274773141325</v>
+        <v>359.1400512084888</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36447,28 +36551,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1528014624578205</v>
+        <v>-0.1546175621137864</v>
       </c>
       <c r="J5" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K5" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1249473778125878</v>
+        <v>0.1278068197160662</v>
       </c>
       <c r="M5" t="n">
-        <v>2.148136419070438</v>
+        <v>2.151219417167378</v>
       </c>
       <c r="N5" t="n">
-        <v>7.848159869333815</v>
+        <v>7.852196122545571</v>
       </c>
       <c r="O5" t="n">
-        <v>2.801456740578697</v>
+        <v>2.802177032691827</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0727649082831</v>
+        <v>361.0939581005196</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36529,28 +36633,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1084979850482826</v>
+        <v>-0.1115229786724825</v>
       </c>
       <c r="J6" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K6" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05350308964445472</v>
+        <v>0.05626026669921114</v>
       </c>
       <c r="M6" t="n">
-        <v>2.455992651923155</v>
+        <v>2.46477515087937</v>
       </c>
       <c r="N6" t="n">
-        <v>9.995153761349068</v>
+        <v>10.04139408380365</v>
       </c>
       <c r="O6" t="n">
-        <v>3.161511309698112</v>
+        <v>3.168815880388705</v>
       </c>
       <c r="P6" t="n">
-        <v>358.5702949553074</v>
+        <v>358.605596026234</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36611,28 +36715,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07913861165286176</v>
+        <v>-0.08303071060853548</v>
       </c>
       <c r="J7" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K7" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03440227276314056</v>
+        <v>0.03740973278259485</v>
       </c>
       <c r="M7" t="n">
-        <v>2.214853198320633</v>
+        <v>2.231176468208044</v>
       </c>
       <c r="N7" t="n">
-        <v>8.437071883357921</v>
+        <v>8.537863495097969</v>
       </c>
       <c r="O7" t="n">
-        <v>2.904663815892972</v>
+        <v>2.921962267911407</v>
       </c>
       <c r="P7" t="n">
-        <v>357.065679067755</v>
+        <v>357.1110988856906</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36693,28 +36797,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0207859299664831</v>
+        <v>0.01733802269817333</v>
       </c>
       <c r="J8" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K8" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002494289281442907</v>
+        <v>0.001726187828045012</v>
       </c>
       <c r="M8" t="n">
-        <v>2.177135993176999</v>
+        <v>2.190117445480535</v>
       </c>
       <c r="N8" t="n">
-        <v>8.293030923542743</v>
+        <v>8.3671123394068</v>
       </c>
       <c r="O8" t="n">
-        <v>2.879762303306081</v>
+        <v>2.892596124488657</v>
       </c>
       <c r="P8" t="n">
-        <v>356.2995630304601</v>
+        <v>356.3397994096891</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -36775,28 +36879,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08992044238491588</v>
+        <v>0.08720887944944365</v>
       </c>
       <c r="J9" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K9" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03333618806630734</v>
+        <v>0.03142857903140539</v>
       </c>
       <c r="M9" t="n">
-        <v>2.528842074292162</v>
+        <v>2.534152601712408</v>
       </c>
       <c r="N9" t="n">
-        <v>11.25335936757348</v>
+        <v>11.28088454142796</v>
       </c>
       <c r="O9" t="n">
-        <v>3.354602713820741</v>
+        <v>3.358702806356638</v>
       </c>
       <c r="P9" t="n">
-        <v>361.9895543085614</v>
+        <v>362.0211979545611</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -36857,28 +36961,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1321905032637029</v>
+        <v>0.1293739981767294</v>
       </c>
       <c r="J10" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K10" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05953683252438502</v>
+        <v>0.05721312740842088</v>
       </c>
       <c r="M10" t="n">
-        <v>2.741893151412646</v>
+        <v>2.746213575624174</v>
       </c>
       <c r="N10" t="n">
-        <v>13.24836769326075</v>
+        <v>13.27475992438456</v>
       </c>
       <c r="O10" t="n">
-        <v>3.639830723160179</v>
+        <v>3.643454394442801</v>
       </c>
       <c r="P10" t="n">
-        <v>345.1914380142589</v>
+        <v>345.2243062803103</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -36939,28 +37043,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1612493495224513</v>
+        <v>0.1578519139540915</v>
       </c>
       <c r="J11" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K11" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07776604438323698</v>
+        <v>0.0747170366997536</v>
       </c>
       <c r="M11" t="n">
-        <v>2.925120475243709</v>
+        <v>2.931066879931931</v>
       </c>
       <c r="N11" t="n">
-        <v>14.79969745860139</v>
+        <v>14.85147087483719</v>
       </c>
       <c r="O11" t="n">
-        <v>3.847037491187392</v>
+        <v>3.853760614625303</v>
       </c>
       <c r="P11" t="n">
-        <v>338.7810322749912</v>
+        <v>338.8206801254063</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37002,7 +37106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L669"/>
+  <dimension ref="A1:L671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78483,6 +78587,130 @@
         </is>
       </c>
     </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-36.77813834621838,175.0093587969536</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-36.77886893022412,175.00931220960885</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-36.77955321383445,175.00958485373195</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-36.780208088174504,175.00998536987692</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-36.78080762682115,175.0104906456994</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-36.78135810494185,175.0110784398704</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-36.78187558501138,175.0117036220913</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-36.78234667085153,175.0123861380125</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-36.782788658608744,175.01312063751678</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>-36.78315412685276,175.0138991873839</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-36.778138266058775,175.00936607761238</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-36.77886810550191,175.00931862546707</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-36.77955202540666,175.0095884855261</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-36.78020694734576,175.00998765395303</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-36.78080693137481,175.01049167509905</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-36.781356510194826,175.01108057365403</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-36.781874658160575,175.01170484521379</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-36.78234681736789,175.01238600754502</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-36.78278857689665,175.01312068474644</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>-36.78315494397537,175.0138987150904</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L671"/>
+  <dimension ref="A1:L672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28628,6 +28628,48 @@
         <v>337.28</v>
       </c>
       <c r="L671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="C672" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="D672" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="E672" t="n">
+        <v>356.94</v>
+      </c>
+      <c r="F672" t="n">
+        <v>354.17</v>
+      </c>
+      <c r="G672" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="H672" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="I672" t="n">
+        <v>358.78</v>
+      </c>
+      <c r="J672" t="n">
+        <v>342.71</v>
+      </c>
+      <c r="K672" t="n">
+        <v>335.87</v>
+      </c>
+      <c r="L672" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28644,7 +28686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B749"/>
+  <dimension ref="A1:B750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36137,6 +36179,16 @@
       </c>
       <c r="B749" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -36305,34 +36357,30 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1562613044495569</v>
+        <v>-0.1539337919936888</v>
       </c>
       <c r="J2" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K2" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1197192565268114</v>
+        <v>0.1158351199101832</v>
       </c>
       <c r="M2" t="n">
-        <v>2.363638636841922</v>
+        <v>2.372550166453224</v>
       </c>
       <c r="N2" t="n">
-        <v>8.64121714157706</v>
+        <v>8.717594947551552</v>
       </c>
       <c r="O2" t="n">
-        <v>2.939594724035451</v>
+        <v>2.952557357199272</v>
       </c>
       <c r="P2" t="n">
-        <v>356.1346119113899</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>356.1073304034816</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (175.00536787040522 -36.77818221896405, 175.01568087835767 -36.77806857258912)</t>
@@ -36387,34 +36435,30 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.13434688298891</v>
+        <v>-0.1348420347979881</v>
       </c>
       <c r="J3" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K3" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147663220912347</v>
+        <v>0.1157529467021475</v>
       </c>
       <c r="M3" t="n">
-        <v>1.880402785286566</v>
+        <v>1.880066201475225</v>
       </c>
       <c r="N3" t="n">
-        <v>6.700596875683834</v>
+        <v>6.694650409279927</v>
       </c>
       <c r="O3" t="n">
-        <v>2.588551115138319</v>
+        <v>2.587402251154607</v>
       </c>
       <c r="P3" t="n">
-        <v>359.5358027700044</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>359.5416066005966</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (175.0054169810171 -36.77936957295913, 175.01560141580842 -36.77806031470136)</t>
@@ -36469,34 +36513,30 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1394092953899895</v>
+        <v>-0.1389693523343062</v>
       </c>
       <c r="J4" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K4" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0903477217152574</v>
+        <v>0.09004086551840385</v>
       </c>
       <c r="M4" t="n">
-        <v>2.211916685973201</v>
+        <v>2.210712671906482</v>
       </c>
       <c r="N4" t="n">
-        <v>9.41795275788297</v>
+        <v>9.407105997899377</v>
       </c>
       <c r="O4" t="n">
-        <v>3.068868318759046</v>
+        <v>3.067100584900889</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1400512084888</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>359.1348944971155</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (175.0059165783527 -36.78075350483464, 175.01546837438747 -36.7776277648029)</t>
@@ -36551,34 +36591,30 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1546175621137864</v>
+        <v>-0.1546408014610663</v>
       </c>
       <c r="J5" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K5" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1278068197160662</v>
+        <v>0.1281662531687777</v>
       </c>
       <c r="M5" t="n">
-        <v>2.151219417167378</v>
+        <v>2.148133907848054</v>
       </c>
       <c r="N5" t="n">
-        <v>7.852196122545571</v>
+        <v>7.840502791028334</v>
       </c>
       <c r="O5" t="n">
-        <v>2.802177032691827</v>
+        <v>2.800089782672751</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0939581005196</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>361.0942304962419</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (175.00661732939344 -36.78189024196106, 175.0153760437372 -36.777515392336994)</t>
@@ -36633,34 +36669,30 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1115229786724825</v>
+        <v>-0.1119716279645538</v>
       </c>
       <c r="J6" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K6" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05626026669921114</v>
+        <v>0.05682680719942845</v>
       </c>
       <c r="M6" t="n">
-        <v>2.46477515087937</v>
+        <v>2.46347442258905</v>
       </c>
       <c r="N6" t="n">
-        <v>10.04139408380365</v>
+        <v>10.02974566468924</v>
       </c>
       <c r="O6" t="n">
-        <v>3.168815880388705</v>
+        <v>3.166977370410032</v>
       </c>
       <c r="P6" t="n">
-        <v>358.605596026234</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>358.6108547861511</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (175.00748308885855 -36.782839395255266, 175.0153762946955 -36.77750672117123)</t>
@@ -36715,34 +36747,30 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08303071060853548</v>
+        <v>-0.08458168856470494</v>
       </c>
       <c r="J7" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K7" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03740973278259485</v>
+        <v>0.03870176134886505</v>
       </c>
       <c r="M7" t="n">
-        <v>2.231176468208044</v>
+        <v>2.237006755498212</v>
       </c>
       <c r="N7" t="n">
-        <v>8.537863495097969</v>
+        <v>8.564773074954703</v>
       </c>
       <c r="O7" t="n">
-        <v>2.921962267911407</v>
+        <v>2.926563355704896</v>
       </c>
       <c r="P7" t="n">
-        <v>357.1110988856906</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>357.1292783877036</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (175.0082196645776 -36.783494604241504, 175.01577047898564 -36.77785112187208)</t>
@@ -36797,34 +36825,30 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01733802269817333</v>
+        <v>0.0156297804739823</v>
       </c>
       <c r="J8" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K8" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001726187828045012</v>
+        <v>0.001399308269440458</v>
       </c>
       <c r="M8" t="n">
-        <v>2.190117445480535</v>
+        <v>2.196477145389012</v>
       </c>
       <c r="N8" t="n">
-        <v>8.3671123394068</v>
+        <v>8.402721336057331</v>
       </c>
       <c r="O8" t="n">
-        <v>2.892596124488657</v>
+        <v>2.898744786292393</v>
       </c>
       <c r="P8" t="n">
-        <v>356.3397994096891</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>356.3598222558101</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (175.0088415160924 -36.78404432167193, 175.01634374107144 -36.77835917592822)</t>
@@ -36879,34 +36903,30 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08720887944944365</v>
+        <v>0.08554443164855935</v>
       </c>
       <c r="J9" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K9" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03142857903140539</v>
+        <v>0.0302433734077201</v>
       </c>
       <c r="M9" t="n">
-        <v>2.534152601712408</v>
+        <v>2.538419446979109</v>
       </c>
       <c r="N9" t="n">
-        <v>11.28088454142796</v>
+        <v>11.30971751082285</v>
       </c>
       <c r="O9" t="n">
-        <v>3.358702806356638</v>
+        <v>3.362992344746394</v>
       </c>
       <c r="P9" t="n">
-        <v>362.0211979545611</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>362.0407074724278</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (175.0100388180766 -36.784982625228146, 175.0160389061506 -36.7782443064771)</t>
@@ -36961,34 +36981,30 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1293739981767294</v>
+        <v>0.1275935104180046</v>
       </c>
       <c r="J10" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K10" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05721312740842088</v>
+        <v>0.05568314071715108</v>
       </c>
       <c r="M10" t="n">
-        <v>2.746213575624174</v>
+        <v>2.749994197054223</v>
       </c>
       <c r="N10" t="n">
-        <v>13.27475992438456</v>
+        <v>13.30720769815157</v>
       </c>
       <c r="O10" t="n">
-        <v>3.643454394442801</v>
+        <v>3.647904562642994</v>
       </c>
       <c r="P10" t="n">
-        <v>345.2243062803103</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>345.2451759391375</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (175.0114961622814 -36.78559905423668, 175.01583918136063 -36.77808499899458)</t>
@@ -37043,34 +37059,30 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1578519139540915</v>
+        <v>0.1557156066882365</v>
       </c>
       <c r="J11" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K11" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0747170366997536</v>
+        <v>0.07271048782521206</v>
       </c>
       <c r="M11" t="n">
-        <v>2.931066879931931</v>
+        <v>2.935865202029791</v>
       </c>
       <c r="N11" t="n">
-        <v>14.85147087483719</v>
+        <v>14.90453106244894</v>
       </c>
       <c r="O11" t="n">
-        <v>3.853760614625303</v>
+        <v>3.860638685819866</v>
       </c>
       <c r="P11" t="n">
-        <v>338.8206801254063</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>338.8457204569503</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>LINESTRING (175.0123057082488 -36.785910925577184, 175.01664868500148 -36.77839686339278)</t>
@@ -37106,7 +37118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L671"/>
+  <dimension ref="A1:L672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78711,6 +78723,68 @@
         </is>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-36.77813791828426,175.00939766447016</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-36.77886578774631,175.0093366562403</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-36.77954160119246,175.00962034154412</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-36.780193590139376,175.01001439667237</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-36.7807868793353,175.010521356114</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-36.78134939516923,175.01109009361073</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-36.781874843530744,175.0117046005893</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-36.78235428970159,175.01237935370264</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-36.782798709195426,175.01311482826486</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>-36.78316646540402,175.01389205575086</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L672"/>
+  <dimension ref="A1:L675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28672,6 +28672,132 @@
       <c r="L672" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="C673" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="D673" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="E673" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="F673" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="G673" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="H673" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="I673" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="J673" t="n">
+        <v>342.74</v>
+      </c>
+      <c r="K673" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="C674" t="n">
+        <v>355.33</v>
+      </c>
+      <c r="D674" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="E674" t="n">
+        <v>358.11</v>
+      </c>
+      <c r="F674" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="G674" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="H674" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="I674" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="J674" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="K674" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="C675" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="D675" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="E675" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="F675" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="G675" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="H675" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="I675" t="n">
+        <v>359.52</v>
+      </c>
+      <c r="J675" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="K675" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28686,7 +28812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B750"/>
+  <dimension ref="A1:B753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36189,6 +36315,36 @@
       </c>
       <c r="B750" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -36357,28 +36513,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1539337919936888</v>
+        <v>-0.1475267727610528</v>
       </c>
       <c r="J2" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K2" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1158351199101832</v>
+        <v>0.1057675390443767</v>
       </c>
       <c r="M2" t="n">
-        <v>2.372550166453224</v>
+        <v>2.396712359643872</v>
       </c>
       <c r="N2" t="n">
-        <v>8.717594947551552</v>
+        <v>8.907607256544427</v>
       </c>
       <c r="O2" t="n">
-        <v>2.952557357199272</v>
+        <v>2.984561484798802</v>
       </c>
       <c r="P2" t="n">
-        <v>356.1073304034816</v>
+        <v>356.0319846757556</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36435,28 +36591,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1348420347979881</v>
+        <v>-0.1364387921656112</v>
       </c>
       <c r="J3" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K3" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1157529467021475</v>
+        <v>0.1186900487245531</v>
       </c>
       <c r="M3" t="n">
-        <v>1.880066201475225</v>
+        <v>1.879579893251362</v>
       </c>
       <c r="N3" t="n">
-        <v>6.694650409279927</v>
+        <v>6.6913145041304</v>
       </c>
       <c r="O3" t="n">
-        <v>2.587402251154607</v>
+        <v>2.586757527123561</v>
       </c>
       <c r="P3" t="n">
-        <v>359.5416066005966</v>
+        <v>359.5604036877918</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36513,28 +36669,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1389693523343062</v>
+        <v>-0.1375656739680377</v>
       </c>
       <c r="J4" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K4" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09004086551840385</v>
+        <v>0.08893759221797803</v>
       </c>
       <c r="M4" t="n">
-        <v>2.210712671906482</v>
+        <v>2.20867308654559</v>
       </c>
       <c r="N4" t="n">
-        <v>9.407105997899377</v>
+        <v>9.384351466270012</v>
       </c>
       <c r="O4" t="n">
-        <v>3.067100584900889</v>
+        <v>3.063388885902345</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1348944971155</v>
+        <v>359.1183988232594</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36591,28 +36747,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1546408014610663</v>
+        <v>-0.1543522405503175</v>
       </c>
       <c r="J5" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K5" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1281662531687777</v>
+        <v>0.1286213454138209</v>
       </c>
       <c r="M5" t="n">
-        <v>2.148133907848054</v>
+        <v>2.144362104112087</v>
       </c>
       <c r="N5" t="n">
-        <v>7.840502791028334</v>
+        <v>7.81341856327076</v>
       </c>
       <c r="O5" t="n">
-        <v>2.800089782672751</v>
+        <v>2.79524928463827</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0942304962419</v>
+        <v>361.0908497846144</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36669,28 +36825,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1119716279645538</v>
+        <v>-0.1131203622066623</v>
       </c>
       <c r="J6" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K6" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05682680719942845</v>
+        <v>0.0583284381608874</v>
       </c>
       <c r="M6" t="n">
-        <v>2.46347442258905</v>
+        <v>2.458490417811151</v>
       </c>
       <c r="N6" t="n">
-        <v>10.02974566468924</v>
+        <v>10.00050719011995</v>
       </c>
       <c r="O6" t="n">
-        <v>3.166977370410032</v>
+        <v>3.162357852950856</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6108547861511</v>
+        <v>358.6243795733597</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36747,28 +36903,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08458168856470494</v>
+        <v>-0.08886986538840025</v>
       </c>
       <c r="J7" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K7" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03870176134886505</v>
+        <v>0.0424220901670761</v>
       </c>
       <c r="M7" t="n">
-        <v>2.237006755498212</v>
+        <v>2.252342341832875</v>
       </c>
       <c r="N7" t="n">
-        <v>8.564773074954703</v>
+        <v>8.630032788174606</v>
       </c>
       <c r="O7" t="n">
-        <v>2.926563355704896</v>
+        <v>2.937691744920594</v>
       </c>
       <c r="P7" t="n">
-        <v>357.1292783877036</v>
+        <v>357.1797225780855</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36825,28 +36981,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0156297804739823</v>
+        <v>0.0102569183665177</v>
       </c>
       <c r="J8" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K8" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001399308269440458</v>
+        <v>0.0005971009468555</v>
       </c>
       <c r="M8" t="n">
-        <v>2.196477145389012</v>
+        <v>2.216957155405624</v>
       </c>
       <c r="N8" t="n">
-        <v>8.402721336057331</v>
+        <v>8.524089244939482</v>
       </c>
       <c r="O8" t="n">
-        <v>2.898744786292393</v>
+        <v>2.919604295951676</v>
       </c>
       <c r="P8" t="n">
-        <v>356.3598222558101</v>
+        <v>356.4230207593671</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36903,28 +37059,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08554443164855935</v>
+        <v>0.08110181256201179</v>
       </c>
       <c r="J9" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K9" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0302433734077201</v>
+        <v>0.02724687296267359</v>
       </c>
       <c r="M9" t="n">
-        <v>2.538419446979109</v>
+        <v>2.548793642356084</v>
       </c>
       <c r="N9" t="n">
-        <v>11.30971751082285</v>
+        <v>11.36759086955137</v>
       </c>
       <c r="O9" t="n">
-        <v>3.362992344746394</v>
+        <v>3.371585809311602</v>
       </c>
       <c r="P9" t="n">
-        <v>362.0407074724278</v>
+        <v>362.0929577286082</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36981,28 +37137,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1275935104180046</v>
+        <v>0.1228150983971198</v>
       </c>
       <c r="J10" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K10" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05568314071715108</v>
+        <v>0.05177100797196832</v>
       </c>
       <c r="M10" t="n">
-        <v>2.749994197054223</v>
+        <v>2.759012454438481</v>
       </c>
       <c r="N10" t="n">
-        <v>13.30720769815157</v>
+        <v>13.37369686203925</v>
       </c>
       <c r="O10" t="n">
-        <v>3.647904562642994</v>
+        <v>3.657006543887944</v>
       </c>
       <c r="P10" t="n">
-        <v>345.2451759391375</v>
+        <v>345.3013731772429</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37059,28 +37215,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1557156066882365</v>
+        <v>0.1505304210611524</v>
       </c>
       <c r="J11" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K11" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07271048782521206</v>
+        <v>0.0682052418085316</v>
       </c>
       <c r="M11" t="n">
-        <v>2.935865202029791</v>
+        <v>2.944953726606943</v>
       </c>
       <c r="N11" t="n">
-        <v>14.90453106244894</v>
+        <v>14.98554036390211</v>
       </c>
       <c r="O11" t="n">
-        <v>3.860638685819866</v>
+        <v>3.871116165126295</v>
       </c>
       <c r="P11" t="n">
-        <v>338.8457204569503</v>
+        <v>338.9067051581607</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37118,7 +37274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L672"/>
+  <dimension ref="A1:L675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78785,6 +78941,192 @@
         </is>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-36.77813786032103,175.00940292894637</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-36.77886423783461,175.0093487136278</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-36.779537662399285,175.00963237834338</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-36.78018684023217,175.01002791078318</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-36.78077957714576,175.0105321648034</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-36.78134313885301,175.01109846460568</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-36.78187397847,175.01170574217025</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-36.782351872181884,175.0123815064165</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-36.78279846405916,175.01311496995396</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>-36.78315764047999,175.01389715652175</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-36.77813796884775,175.0093930720547</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-36.77886438002839,175.00934760744548</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-36.779538341501635,175.00963030303328</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-36.78018802859623,175.0100255315385</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-36.78078073622353,175.01053044913857</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-36.7813444882546,175.01109665909706</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-36.781876450072104,175.0117024805103</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-36.7823496744367,175.01238346342896</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-36.78279225394059,175.01311855941057</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>-36.78315412685276,175.0138991873839</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-36.77813814150221,175.009377390636</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-36.77886938524312,175.00930866982495</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-36.779547814975864,175.00960135245302</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-36.78020038757964,175.01000078738934</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-36.78079684740205,175.01050660139174</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-36.78135405673781,175.01108385639793</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-36.781880281055194,175.01169742493693</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-36.78234886859678,175.01238418100016</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-36.782791273395546,175.01311912616683</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>-36.78315559767345,175.0138983372556</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L675"/>
+  <dimension ref="A1:L676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28798,6 +28798,48 @@
       <c r="L675" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="C676" t="n">
+        <v>352.06</v>
+      </c>
+      <c r="D676" t="n">
+        <v>355.41</v>
+      </c>
+      <c r="E676" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="F676" t="n">
+        <v>353.42</v>
+      </c>
+      <c r="G676" t="n">
+        <v>351.62</v>
+      </c>
+      <c r="H676" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="I676" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="J676" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="K676" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28812,7 +28854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B753"/>
+  <dimension ref="A1:B754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36345,6 +36387,16 @@
       </c>
       <c r="B753" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -36513,28 +36565,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1475267727610528</v>
+        <v>-0.146181921552047</v>
       </c>
       <c r="J2" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K2" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1057675390443767</v>
+        <v>0.1040083616653154</v>
       </c>
       <c r="M2" t="n">
-        <v>2.396712359643872</v>
+        <v>2.400610615773874</v>
       </c>
       <c r="N2" t="n">
-        <v>8.907607256544427</v>
+        <v>8.924283273083773</v>
       </c>
       <c r="O2" t="n">
-        <v>2.984561484798802</v>
+        <v>2.987353891503946</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0319846757556</v>
+        <v>356.0161315571496</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36591,28 +36643,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1364387921656112</v>
+        <v>-0.137599980965308</v>
       </c>
       <c r="J3" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K3" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1186900487245531</v>
+        <v>0.1204324475371427</v>
       </c>
       <c r="M3" t="n">
-        <v>1.879579893251362</v>
+        <v>1.88261321642201</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6913145041304</v>
+        <v>6.703671863155932</v>
       </c>
       <c r="O3" t="n">
-        <v>2.586757527123561</v>
+        <v>2.589145006204931</v>
       </c>
       <c r="P3" t="n">
-        <v>359.5604036877918</v>
+        <v>359.5740917922025</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36669,28 +36721,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1375656739680377</v>
+        <v>-0.1375836734209098</v>
       </c>
       <c r="J4" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K4" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08893759221797803</v>
+        <v>0.08919656652363961</v>
       </c>
       <c r="M4" t="n">
-        <v>2.20867308654559</v>
+        <v>2.205492690617643</v>
       </c>
       <c r="N4" t="n">
-        <v>9.384351466270012</v>
+        <v>9.370454074435147</v>
       </c>
       <c r="O4" t="n">
-        <v>3.063388885902345</v>
+        <v>3.061119741930254</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1183988232594</v>
+        <v>359.118611000978</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36747,28 +36799,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1543522405503175</v>
+        <v>-0.1543433760673985</v>
       </c>
       <c r="J5" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K5" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1286213454138209</v>
+        <v>0.1289372648181689</v>
       </c>
       <c r="M5" t="n">
-        <v>2.144362104112087</v>
+        <v>2.141226927979894</v>
       </c>
       <c r="N5" t="n">
-        <v>7.81341856327076</v>
+        <v>7.801844426227137</v>
       </c>
       <c r="O5" t="n">
-        <v>2.79524928463827</v>
+        <v>2.793178194499438</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0908497846144</v>
+        <v>361.090745290007</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36825,28 +36877,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1131203622066623</v>
+        <v>-0.1137793992924476</v>
       </c>
       <c r="J6" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K6" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0583284381608874</v>
+        <v>0.05909277127364598</v>
       </c>
       <c r="M6" t="n">
-        <v>2.458490417811151</v>
+        <v>2.458263985841644</v>
       </c>
       <c r="N6" t="n">
-        <v>10.00050719011995</v>
+        <v>9.99286531038436</v>
       </c>
       <c r="O6" t="n">
-        <v>3.162357852950856</v>
+        <v>3.161149365402458</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6243795733597</v>
+        <v>358.6321483086791</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36903,28 +36955,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08886986538840025</v>
+        <v>-0.08982560055327309</v>
       </c>
       <c r="J7" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K7" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0424220901670761</v>
+        <v>0.0433486909947477</v>
       </c>
       <c r="M7" t="n">
-        <v>2.252342341832875</v>
+        <v>2.254719426883969</v>
       </c>
       <c r="N7" t="n">
-        <v>8.630032788174606</v>
+        <v>8.632334378083792</v>
       </c>
       <c r="O7" t="n">
-        <v>2.937691744920594</v>
+        <v>2.938083453219767</v>
       </c>
       <c r="P7" t="n">
-        <v>357.1797225780855</v>
+        <v>357.1909887931308</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36981,28 +37033,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0102569183665177</v>
+        <v>0.009090379385138091</v>
       </c>
       <c r="J8" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K8" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005971009468555</v>
+        <v>0.0004692033175023314</v>
       </c>
       <c r="M8" t="n">
-        <v>2.216957155405624</v>
+        <v>2.220324965077467</v>
       </c>
       <c r="N8" t="n">
-        <v>8.524089244939482</v>
+        <v>8.533937076969709</v>
       </c>
       <c r="O8" t="n">
-        <v>2.919604295951676</v>
+        <v>2.921290310285801</v>
       </c>
       <c r="P8" t="n">
-        <v>356.4230207593671</v>
+        <v>356.4367719317693</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37059,28 +37111,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08110181256201179</v>
+        <v>0.07982904546006003</v>
       </c>
       <c r="J9" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K9" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02724687296267359</v>
+        <v>0.02643563716675412</v>
       </c>
       <c r="M9" t="n">
-        <v>2.548793642356084</v>
+        <v>2.55126279691961</v>
       </c>
       <c r="N9" t="n">
-        <v>11.36759086955137</v>
+        <v>11.37750595591162</v>
       </c>
       <c r="O9" t="n">
-        <v>3.371585809311602</v>
+        <v>3.373055877970542</v>
       </c>
       <c r="P9" t="n">
-        <v>362.0929577286082</v>
+        <v>362.1079611190873</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37137,28 +37189,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1228150983971198</v>
+        <v>0.1213641492904149</v>
       </c>
       <c r="J10" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K10" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05177100797196832</v>
+        <v>0.0506324068553522</v>
       </c>
       <c r="M10" t="n">
-        <v>2.759012454438481</v>
+        <v>2.761412015896322</v>
       </c>
       <c r="N10" t="n">
-        <v>13.37369686203925</v>
+        <v>13.38865576733519</v>
       </c>
       <c r="O10" t="n">
-        <v>3.657006543887944</v>
+        <v>3.659051211357281</v>
       </c>
       <c r="P10" t="n">
-        <v>345.3013731772429</v>
+        <v>345.3184769788573</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37215,28 +37267,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1505304210611524</v>
+        <v>0.1488760565283092</v>
       </c>
       <c r="J11" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K11" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0682052418085316</v>
+        <v>0.06680857245066973</v>
       </c>
       <c r="M11" t="n">
-        <v>2.944953726606943</v>
+        <v>2.947727564454374</v>
       </c>
       <c r="N11" t="n">
-        <v>14.98554036390211</v>
+        <v>15.00854442092525</v>
       </c>
       <c r="O11" t="n">
-        <v>3.871116165126295</v>
+        <v>3.874086269164028</v>
       </c>
       <c r="P11" t="n">
-        <v>338.9067051581607</v>
+        <v>338.9262068227175</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37274,7 +37326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L675"/>
+  <dimension ref="A1:L676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79127,6 +79179,68 @@
         </is>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-36.77813830675525,175.00936238127792</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-36.77886902975955,175.00931143528112</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-36.77954676236795,175.00960456918452</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-36.7801931623284,175.0100152532006</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-36.78079122587626,175.0105149223693</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-36.78133792525574,175.01110544043377</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-36.78186446280113,175.01171829955916</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-36.78234542546256,175.0123872469861</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-36.782790619698844,175.01311950400432</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>-36.78315429027729,175.0138990929252</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L676"/>
+  <dimension ref="A1:L682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28840,6 +28840,258 @@
       <c r="L676" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="C677" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="D677" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="E677" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="F677" t="n">
+        <v>351.31</v>
+      </c>
+      <c r="G677" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="H677" t="n">
+        <v>352.92</v>
+      </c>
+      <c r="I677" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="J677" t="n">
+        <v>344.49</v>
+      </c>
+      <c r="K677" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="C678" t="n">
+        <v>350.54</v>
+      </c>
+      <c r="D678" t="n">
+        <v>351.51</v>
+      </c>
+      <c r="E678" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="F678" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="G678" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="H678" t="n">
+        <v>353.08</v>
+      </c>
+      <c r="I678" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="J678" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="K678" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="C679" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="D679" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="E679" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="F679" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="G679" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="H679" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="I679" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="J679" t="n">
+        <v>344.62</v>
+      </c>
+      <c r="K679" t="n">
+        <v>338.17</v>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="C680" t="n">
+        <v>351.84</v>
+      </c>
+      <c r="D680" t="n">
+        <v>352.36</v>
+      </c>
+      <c r="E680" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="F680" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="G680" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="H680" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="I680" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="J680" t="n">
+        <v>344.59</v>
+      </c>
+      <c r="K680" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="C681" t="n">
+        <v>351.89</v>
+      </c>
+      <c r="D681" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="E681" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="F681" t="n">
+        <v>352.38</v>
+      </c>
+      <c r="G681" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="H681" t="n">
+        <v>353.82</v>
+      </c>
+      <c r="I681" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="J681" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="K681" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="C682" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="D682" t="n">
+        <v>354.19</v>
+      </c>
+      <c r="E682" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="F682" t="n">
+        <v>354.13</v>
+      </c>
+      <c r="G682" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="H682" t="n">
+        <v>354.31</v>
+      </c>
+      <c r="I682" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="J682" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="K682" t="n">
+        <v>338.62</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28854,7 +29106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B754"/>
+  <dimension ref="A1:B760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36397,6 +36649,66 @@
       </c>
       <c r="B754" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -36565,28 +36877,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.146181921552047</v>
+        <v>-0.1470148487367268</v>
       </c>
       <c r="J2" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K2" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1040083616653154</v>
+        <v>0.1066762782020875</v>
       </c>
       <c r="M2" t="n">
-        <v>2.400610615773874</v>
+        <v>2.386065000548055</v>
       </c>
       <c r="N2" t="n">
-        <v>8.924283273083773</v>
+        <v>8.851624651576966</v>
       </c>
       <c r="O2" t="n">
-        <v>2.987353891503946</v>
+        <v>2.975168003924646</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0161315571496</v>
+        <v>356.0259830625313</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36643,28 +36955,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.137599980965308</v>
+        <v>-0.145242865560828</v>
       </c>
       <c r="J3" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K3" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1204324475371427</v>
+        <v>0.1314436398716579</v>
       </c>
       <c r="M3" t="n">
-        <v>1.88261321642201</v>
+        <v>1.904898667398103</v>
       </c>
       <c r="N3" t="n">
-        <v>6.703671863155932</v>
+        <v>6.817224888646446</v>
       </c>
       <c r="O3" t="n">
-        <v>2.589145006204931</v>
+        <v>2.610981594850191</v>
       </c>
       <c r="P3" t="n">
-        <v>359.5740917922025</v>
+        <v>359.6645835617129</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36721,28 +37033,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1375836734209098</v>
+        <v>-0.1432975469990833</v>
       </c>
       <c r="J4" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K4" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08919656652363961</v>
+        <v>0.09665040840964201</v>
       </c>
       <c r="M4" t="n">
-        <v>2.205492690617643</v>
+        <v>2.215126333335274</v>
       </c>
       <c r="N4" t="n">
-        <v>9.370454074435147</v>
+        <v>9.386187958267897</v>
       </c>
       <c r="O4" t="n">
-        <v>3.061119741930254</v>
+        <v>3.0636886196655</v>
       </c>
       <c r="P4" t="n">
-        <v>359.118611000978</v>
+        <v>359.1862619897481</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36799,28 +37111,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1543433760673985</v>
+        <v>-0.1555639975755326</v>
       </c>
       <c r="J5" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K5" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1289372648181689</v>
+        <v>0.1325582457200936</v>
       </c>
       <c r="M5" t="n">
-        <v>2.141226927979894</v>
+        <v>2.131786403738234</v>
       </c>
       <c r="N5" t="n">
-        <v>7.801844426227137</v>
+        <v>7.744820206397598</v>
       </c>
       <c r="O5" t="n">
-        <v>2.793178194499438</v>
+        <v>2.782951707521637</v>
       </c>
       <c r="P5" t="n">
-        <v>361.090745290007</v>
+        <v>361.1051791649048</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36877,28 +37189,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1137793992924476</v>
+        <v>-0.1195021936223842</v>
       </c>
       <c r="J6" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K6" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05909277127364598</v>
+        <v>0.06526444223276273</v>
       </c>
       <c r="M6" t="n">
-        <v>2.458263985841644</v>
+        <v>2.466203508190018</v>
       </c>
       <c r="N6" t="n">
-        <v>9.99286531038436</v>
+        <v>10.00284325177408</v>
       </c>
       <c r="O6" t="n">
-        <v>3.161149365402458</v>
+        <v>3.162727185796157</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6321483086791</v>
+        <v>358.6999048532788</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36955,28 +37267,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08982560055327309</v>
+        <v>-0.09439563322189565</v>
       </c>
       <c r="J7" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K7" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0433486909947477</v>
+        <v>0.04814691894903367</v>
       </c>
       <c r="M7" t="n">
-        <v>2.254719426883969</v>
+        <v>2.262203914069408</v>
       </c>
       <c r="N7" t="n">
-        <v>8.632334378083792</v>
+        <v>8.615188873917349</v>
       </c>
       <c r="O7" t="n">
-        <v>2.938083453219767</v>
+        <v>2.935164198800018</v>
       </c>
       <c r="P7" t="n">
-        <v>357.1909887931308</v>
+        <v>357.2451060280156</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37033,28 +37345,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009090379385138091</v>
+        <v>0.003598832541416782</v>
       </c>
       <c r="J8" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K8" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004692033175023314</v>
+        <v>7.413189758265215e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.220324965077467</v>
+        <v>2.231763235834273</v>
       </c>
       <c r="N8" t="n">
-        <v>8.533937076969709</v>
+        <v>8.543691136607556</v>
       </c>
       <c r="O8" t="n">
-        <v>2.921290310285801</v>
+        <v>2.922959311486829</v>
       </c>
       <c r="P8" t="n">
-        <v>356.4367719317693</v>
+        <v>356.5018003309289</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37111,28 +37423,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07982904546006003</v>
+        <v>0.07306692066148709</v>
       </c>
       <c r="J9" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K9" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02643563716675412</v>
+        <v>0.02238333367504541</v>
       </c>
       <c r="M9" t="n">
-        <v>2.55126279691961</v>
+        <v>2.561482218645467</v>
       </c>
       <c r="N9" t="n">
-        <v>11.37750595591162</v>
+        <v>11.40367976103903</v>
       </c>
       <c r="O9" t="n">
-        <v>3.373055877970542</v>
+        <v>3.376933484840799</v>
       </c>
       <c r="P9" t="n">
-        <v>362.1079611190873</v>
+        <v>362.1880440427431</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37189,28 +37501,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1213641492904149</v>
+        <v>0.1145728220995166</v>
       </c>
       <c r="J10" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K10" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0506324068553522</v>
+        <v>0.04572421504820989</v>
       </c>
       <c r="M10" t="n">
-        <v>2.761412015896322</v>
+        <v>2.766822106363581</v>
       </c>
       <c r="N10" t="n">
-        <v>13.38865576733519</v>
+        <v>13.39832294477916</v>
       </c>
       <c r="O10" t="n">
-        <v>3.659051211357281</v>
+        <v>3.660371968090013</v>
       </c>
       <c r="P10" t="n">
-        <v>345.3184769788573</v>
+        <v>345.3989060280531</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37267,28 +37579,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1488760565283092</v>
+        <v>0.1405634278189526</v>
       </c>
       <c r="J11" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K11" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06680857245066973</v>
+        <v>0.06026591405051684</v>
       </c>
       <c r="M11" t="n">
-        <v>2.947727564454374</v>
+        <v>2.9570357336345</v>
       </c>
       <c r="N11" t="n">
-        <v>15.00854442092525</v>
+        <v>15.06737115277932</v>
       </c>
       <c r="O11" t="n">
-        <v>3.874086269164028</v>
+        <v>3.881671180404043</v>
       </c>
       <c r="P11" t="n">
-        <v>338.9262068227175</v>
+        <v>339.0246516367424</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37326,7 +37638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L676"/>
+  <dimension ref="A1:L682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79241,6 +79553,378 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-36.778138978847,175.00930133575287</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-36.77887151814329,175.0092920770872</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-36.77956075185972,175.00956181777775</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-36.78020133827048,175.00999888399292</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-36.780803454143026,175.01049682209697</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-36.7813375572371,175.0111059328451</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-36.78186365953033,175.01171935959835</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-36.782346084786134,175.01238665988242</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-36.78278416444388,175.01312323514927</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>-36.78315167548492,175.0139006042644</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-36.77813896281582,175.0093027918847</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-36.778871191098744,175.00929462130705</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-36.779560004848406,175.00956410062028</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-36.78020162347771,175.00999831297398</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-36.78080316437371,175.01049725101345</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-36.7813375572371,175.0111059328451</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-36.781862670889325,175.01172066426193</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-36.78234286142638,175.01238953016693</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>-36.78278457300433,175.01312299900087</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>-36.783149796102904,175.01390169053937</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-36.77813895664998,175.0093033519354</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-36.77887036637748,175.0093010371657</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-36.77955959738766,175.00956534580706</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-36.78019667988514,175.01000821063494</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-36.78079690535593,175.01050651560845</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-36.78133234363941,175.01111290867217</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>-36.781859890336435,175.01172433362805</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>-36.78234205558644,175.012390247738</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>-36.782783102186734,175.0131238491351</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>-36.78314767158407,175.0139029185023</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-36.77813893321974,175.00930548012806</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-36.7788693425851,175.0093090016797</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-36.77955711866792,175.0095729206932</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-36.78019563412507,175.01001030437075</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-36.78079638377108,175.010507287658</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-36.781332711658095,175.0111124162609</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>-36.78185853095497,175.0117261275403</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>-36.78234154277919,175.01239070437416</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>-36.78278334732298,175.01312370744603</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>-36.783147017885966,175.01390329633705</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-36.77813894925095,175.00930402399624</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-36.77886927148837,175.0093095547709</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-36.779557288443236,175.0095724018654</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-36.78019653728149,175.01000849614437</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-36.780797253079164,175.0105060009088</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-36.78133424506921,175.01111036454714</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>-36.781858098424514,175.01172669833053</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>-36.782341909070084,175.01239037820548</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>-36.78278163136912,175.01312469926927</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>-36.78314513850392,175.01390438261188</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-36.77813873591102,175.00932340175032</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-36.77886659825012,175.0093303510007</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-36.77955090488891,175.00959190978907</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-36.78018840887272,175.0100247701802</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-36.78078711115082,175.01052101298097</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-36.781331484929176,175.01111405763183</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>-36.78185507071117,175.01173069386206</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>-36.782339857841094,175.01239220474997</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>-36.78277762747672,175.01312701352327</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>-36.78314399453224,175.01390504382266</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29090,6 +29090,174 @@
         <v>338.62</v>
       </c>
       <c r="L682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>353.76</v>
+      </c>
+      <c r="C683" t="n">
+        <v>355.39</v>
+      </c>
+      <c r="D683" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="E683" t="n">
+        <v>359.19</v>
+      </c>
+      <c r="F683" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="G683" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="H683" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="I683" t="n">
+        <v>362.02</v>
+      </c>
+      <c r="J683" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="K683" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>354.64</v>
+      </c>
+      <c r="C684" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="D684" t="n">
+        <v>356.56</v>
+      </c>
+      <c r="E684" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="F684" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="G684" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="H684" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="I684" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="J684" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="K684" t="n">
+        <v>340.04</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="C685" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="D685" t="n">
+        <v>358</v>
+      </c>
+      <c r="E685" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="F685" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="G685" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="H685" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="I685" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="J685" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="K685" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>352.46</v>
+      </c>
+      <c r="C686" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="D686" t="n">
+        <v>357.85</v>
+      </c>
+      <c r="E686" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="F686" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="G686" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="H686" t="n">
+        <v>354.91</v>
+      </c>
+      <c r="I686" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="J686" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="K686" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="L686" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29106,7 +29274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B760"/>
+  <dimension ref="A1:B764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36709,6 +36877,46 @@
       </c>
       <c r="B760" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>
@@ -36877,28 +37085,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1470148487367268</v>
+        <v>-0.1456361369484181</v>
       </c>
       <c r="J2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1066762782020875</v>
+        <v>0.1058459872707475</v>
       </c>
       <c r="M2" t="n">
-        <v>2.386065000548055</v>
+        <v>2.379842778414311</v>
       </c>
       <c r="N2" t="n">
-        <v>8.851624651576966</v>
+        <v>8.813512854888</v>
       </c>
       <c r="O2" t="n">
-        <v>2.975168003924646</v>
+        <v>2.968756112395897</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0259830625313</v>
+        <v>356.0095922230938</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36955,28 +37163,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.145242865560828</v>
+        <v>-0.1436469801061207</v>
       </c>
       <c r="J3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1314436398716579</v>
+        <v>0.1299081919376767</v>
       </c>
       <c r="M3" t="n">
-        <v>1.904898667398103</v>
+        <v>1.902571611473088</v>
       </c>
       <c r="N3" t="n">
-        <v>6.817224888646446</v>
+        <v>6.798206482101929</v>
       </c>
       <c r="O3" t="n">
-        <v>2.610981594850191</v>
+        <v>2.607337048043833</v>
       </c>
       <c r="P3" t="n">
-        <v>359.6645835617129</v>
+        <v>359.6455880638115</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37033,28 +37241,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1432975469990833</v>
+        <v>-0.1413886134809228</v>
       </c>
       <c r="J4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09665040840964201</v>
+        <v>0.09513773655020796</v>
       </c>
       <c r="M4" t="n">
-        <v>2.215126333335274</v>
+        <v>2.211255865499713</v>
       </c>
       <c r="N4" t="n">
-        <v>9.386187958267897</v>
+        <v>9.352578077354503</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0636886196655</v>
+        <v>3.058198501954133</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1862619897481</v>
+        <v>359.1635468749001</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37111,28 +37319,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1555639975755326</v>
+        <v>-0.152803943672479</v>
       </c>
       <c r="J5" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K5" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1325582457200936</v>
+        <v>0.1293364722821017</v>
       </c>
       <c r="M5" t="n">
-        <v>2.131786403738234</v>
+        <v>2.132461346703898</v>
       </c>
       <c r="N5" t="n">
-        <v>7.744820206397598</v>
+        <v>7.731633804503764</v>
       </c>
       <c r="O5" t="n">
-        <v>2.782951707521637</v>
+        <v>2.780581558685838</v>
       </c>
       <c r="P5" t="n">
-        <v>361.1051791649048</v>
+        <v>361.0723493267264</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37189,28 +37397,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1195021936223842</v>
+        <v>-0.1188789107423945</v>
       </c>
       <c r="J6" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K6" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06526444223276273</v>
+        <v>0.06532311962489412</v>
       </c>
       <c r="M6" t="n">
-        <v>2.466203508190018</v>
+        <v>2.454773012859995</v>
       </c>
       <c r="N6" t="n">
-        <v>10.00284325177408</v>
+        <v>9.946654361588614</v>
       </c>
       <c r="O6" t="n">
-        <v>3.162727185796157</v>
+        <v>3.153831695190568</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6999048532788</v>
+        <v>358.6924892779955</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37267,28 +37475,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09439563322189565</v>
+        <v>-0.09694539739436168</v>
       </c>
       <c r="J7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04814691894903367</v>
+        <v>0.05105742868812901</v>
       </c>
       <c r="M7" t="n">
-        <v>2.262203914069408</v>
+        <v>2.26468472384834</v>
       </c>
       <c r="N7" t="n">
-        <v>8.615188873917349</v>
+        <v>8.592275440538538</v>
       </c>
       <c r="O7" t="n">
-        <v>2.935164198800018</v>
+        <v>2.931258337393437</v>
       </c>
       <c r="P7" t="n">
-        <v>357.2451060280156</v>
+        <v>357.2754340465695</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37345,28 +37553,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003598832541416782</v>
+        <v>0.001667494564164045</v>
       </c>
       <c r="J8" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K8" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L8" t="n">
-        <v>7.413189758265215e-05</v>
+        <v>1.607280785798082e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.231763235834273</v>
+        <v>2.229813503589566</v>
       </c>
       <c r="N8" t="n">
-        <v>8.543691136607556</v>
+        <v>8.509478192849361</v>
       </c>
       <c r="O8" t="n">
-        <v>2.922959311486829</v>
+        <v>2.917100991198172</v>
       </c>
       <c r="P8" t="n">
-        <v>356.5018003309289</v>
+        <v>356.5247729285757</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37423,28 +37631,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07306692066148709</v>
+        <v>0.07089730340429479</v>
       </c>
       <c r="J9" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K9" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02238333367504541</v>
+        <v>0.0213065333892104</v>
       </c>
       <c r="M9" t="n">
-        <v>2.561482218645467</v>
+        <v>2.556966150271237</v>
       </c>
       <c r="N9" t="n">
-        <v>11.40367976103903</v>
+        <v>11.3570656826087</v>
       </c>
       <c r="O9" t="n">
-        <v>3.376933484840799</v>
+        <v>3.370024581899767</v>
       </c>
       <c r="P9" t="n">
-        <v>362.1880440427431</v>
+        <v>362.2138490211719</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37501,28 +37709,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1145728220995166</v>
+        <v>0.1125401617437438</v>
       </c>
       <c r="J10" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K10" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04572421504820989</v>
+        <v>0.04462446368617035</v>
       </c>
       <c r="M10" t="n">
-        <v>2.766822106363581</v>
+        <v>2.759417175556666</v>
       </c>
       <c r="N10" t="n">
-        <v>13.39832294477916</v>
+        <v>13.3379469600524</v>
       </c>
       <c r="O10" t="n">
-        <v>3.660371968090013</v>
+        <v>3.652115408917467</v>
       </c>
       <c r="P10" t="n">
-        <v>345.3989060280531</v>
+        <v>345.4230807488603</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37579,28 +37787,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1405634278189526</v>
+        <v>0.1374934368703698</v>
       </c>
       <c r="J11" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K11" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06026591405051684</v>
+        <v>0.0583046979472025</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9570357336345</v>
+        <v>2.952830894524966</v>
       </c>
       <c r="N11" t="n">
-        <v>15.06737115277932</v>
+        <v>15.01908929352289</v>
       </c>
       <c r="O11" t="n">
-        <v>3.881671180404043</v>
+        <v>3.875446979836376</v>
       </c>
       <c r="P11" t="n">
-        <v>339.0246516367424</v>
+        <v>339.0611665012805</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37638,7 +37846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79925,6 +80133,254 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-36.77813865945317,175.00933034637887</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-36.778864294712136,175.0093482711549</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-36.7795463209517,175.00960591813643</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-36.78018289486319,175.01003580987498</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-36.780779229422436,175.01053267950286</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-36.78133350903189,175.01111134936974</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>-36.781851486887035,175.01173542326632</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>-36.78233055405219,175.01240048943282</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>-36.782768557434615,175.01313225601615</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>-36.78313255481521,175.0139116559291</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-36.778138550931644,175.00934020327097</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-36.77886290121254,175.0093591117414</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-36.77954285753143,175.00961650221996</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-36.7801819441718,175.0100377132705</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-36.780774940834455,175.0105390274623</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-36.78133173027496,175.01111372935765</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>-36.781850868986304,175.01173623868078</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>-36.78232857608125,175.0124022507431</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>-36.78276651463232,175.01313343675764</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>-36.78313239139067,175.01391175038776</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-36.778138846897505,175.00931332083783</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-36.778860199526896,175.00938012920378</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-36.77953796799534,175.00963144445385</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-36.7801819441718,175.0100377132705</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-36.780774940834455,175.0105390274623</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-36.78133173027496,175.01111372935765</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>-36.781850868986304,175.01173623868078</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>-36.78232857608125,175.0124022507431</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>-36.78276651463232,175.01313343675764</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>-36.78313100228216,175.01391255328625</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-36.77813881976756,175.0093157850609</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-36.77885980138343,175.0093832265139</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-36.7795384773221,175.00962988797124</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-36.78018251458665,175.0100365712332</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-36.78077511469613,175.01053877011262</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-36.78133222096654,175.01111307280928</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>-36.78185136330689,175.0117355863492</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>-36.78232674462667,175.01240388158587</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>-36.78276202046721,175.01313603438868</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>-36.78312977659816,175.0139132617261</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
